--- a/관리/WBS(작업분할구조도)_v2.xlsx
+++ b/관리/WBS(작업분할구조도)_v2.xlsx
@@ -571,7 +571,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">기능명세서 116건 검토·합의</t>
+          <t xml:space="preserve">기능명세서 136건 검토·합의</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -709,7 +709,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 45건 내부 우선순위 재정렬</t>
+          <t xml:space="preserve">P1 58건 내부 우선순위 재정렬</t>
         </is>
       </c>
       <c r="E8" s="8"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -7069,8 +7069,585 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7</t>
+        </is>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·근거 (RAG)</t>
+        </is>
+      </c>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="11"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
+      <c r="N112" s="11"/>
+      <c r="O112" s="11"/>
+      <c r="P112" s="11"/>
+      <c r="Q112" s="11"/>
+      <c r="R112" s="11"/>
+      <c r="S112" s="11"/>
+      <c r="T112" s="11"/>
+      <c r="U112" s="11"/>
+      <c r="V112" s="11"/>
+      <c r="W112" s="11"/>
+      <c r="X112" s="11"/>
+      <c r="Y112" s="11"/>
+      <c r="Z112" s="11"/>
+      <c r="AA112" s="11"/>
+      <c r="AB112" s="11"/>
+      <c r="AC112" s="11"/>
+      <c r="AD112" s="11"/>
+      <c r="AE112" s="11"/>
+      <c r="AF112" s="11"/>
+      <c r="AG112" s="11"/>
+      <c r="AH112" s="11"/>
+      <c r="AI112" s="11"/>
+      <c r="AJ112" s="12"/>
+      <c r="AK112" s="12"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7.1</t>
+        </is>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청킹 · 임베딩 · 벡터 인덱스 (리비전 0009)</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-01·RAG-02·RAG-03</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-31</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09-02</t>
+        </is>
+      </c>
+      <c r="I113" s="5">
+        <v>3</v>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드·마이그레이션</t>
+        </is>
+      </c>
+      <c r="K113" s="11"/>
+      <c r="L113" s="11"/>
+      <c r="M113" s="11"/>
+      <c r="N113" s="11"/>
+      <c r="O113" s="11"/>
+      <c r="P113" s="11"/>
+      <c r="Q113" s="11"/>
+      <c r="R113" s="11"/>
+      <c r="S113" s="11"/>
+      <c r="T113" s="11"/>
+      <c r="U113" s="11"/>
+      <c r="V113" s="11"/>
+      <c r="W113" s="11"/>
+      <c r="X113" s="11"/>
+      <c r="Y113" s="11"/>
+      <c r="Z113" s="10"/>
+      <c r="AA113" s="10"/>
+      <c r="AB113" s="10"/>
+      <c r="AC113" s="11"/>
+      <c r="AD113" s="11"/>
+      <c r="AE113" s="11"/>
+      <c r="AF113" s="11"/>
+      <c r="AG113" s="11"/>
+      <c r="AH113" s="11"/>
+      <c r="AI113" s="11"/>
+      <c r="AJ113" s="12"/>
+      <c r="AK113" s="12"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7.2</t>
+        </is>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의미 검색 · 근거 스니펫 · 컨텍스트 조립</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04·RAG-07·RAG-08</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09-02</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09-04</t>
+        </is>
+      </c>
+      <c r="I114" s="5">
+        <v>3</v>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드</t>
+        </is>
+      </c>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="11"/>
+      <c r="P114" s="11"/>
+      <c r="Q114" s="11"/>
+      <c r="R114" s="11"/>
+      <c r="S114" s="11"/>
+      <c r="T114" s="11"/>
+      <c r="U114" s="11"/>
+      <c r="V114" s="11"/>
+      <c r="W114" s="11"/>
+      <c r="X114" s="11"/>
+      <c r="Y114" s="11"/>
+      <c r="Z114" s="11"/>
+      <c r="AA114" s="11"/>
+      <c r="AB114" s="10"/>
+      <c r="AC114" s="10"/>
+      <c r="AD114" s="10"/>
+      <c r="AE114" s="11"/>
+      <c r="AF114" s="11"/>
+      <c r="AG114" s="11"/>
+      <c r="AH114" s="11"/>
+      <c r="AI114" s="11"/>
+      <c r="AJ114" s="12"/>
+      <c r="AK114" s="12"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7.3</t>
+        </is>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검수 확정 시 재임베딩 · 단가 선례 검색</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-09·RAG-12</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09-03</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09-04</t>
+        </is>
+      </c>
+      <c r="I115" s="5">
+        <v>2</v>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드</t>
+        </is>
+      </c>
+      <c r="K115" s="11"/>
+      <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
+      <c r="N115" s="11"/>
+      <c r="O115" s="11"/>
+      <c r="P115" s="11"/>
+      <c r="Q115" s="11"/>
+      <c r="R115" s="11"/>
+      <c r="S115" s="11"/>
+      <c r="T115" s="11"/>
+      <c r="U115" s="11"/>
+      <c r="V115" s="11"/>
+      <c r="W115" s="11"/>
+      <c r="X115" s="11"/>
+      <c r="Y115" s="11"/>
+      <c r="Z115" s="11"/>
+      <c r="AA115" s="11"/>
+      <c r="AB115" s="11"/>
+      <c r="AC115" s="10"/>
+      <c r="AD115" s="10"/>
+      <c r="AE115" s="11"/>
+      <c r="AF115" s="11"/>
+      <c r="AG115" s="11"/>
+      <c r="AH115" s="11"/>
+      <c r="AI115" s="11"/>
+      <c r="AJ115" s="12"/>
+      <c r="AK115" s="12"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8</t>
+        </is>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 계산·검증</t>
+        </is>
+      </c>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="11"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
+      <c r="N116" s="11"/>
+      <c r="O116" s="11"/>
+      <c r="P116" s="11"/>
+      <c r="Q116" s="11"/>
+      <c r="R116" s="11"/>
+      <c r="S116" s="11"/>
+      <c r="T116" s="11"/>
+      <c r="U116" s="11"/>
+      <c r="V116" s="11"/>
+      <c r="W116" s="11"/>
+      <c r="X116" s="11"/>
+      <c r="Y116" s="11"/>
+      <c r="Z116" s="11"/>
+      <c r="AA116" s="11"/>
+      <c r="AB116" s="11"/>
+      <c r="AC116" s="11"/>
+      <c r="AD116" s="11"/>
+      <c r="AE116" s="11"/>
+      <c r="AF116" s="11"/>
+      <c r="AG116" s="11"/>
+      <c r="AH116" s="11"/>
+      <c r="AI116" s="11"/>
+      <c r="AJ116" s="12"/>
+      <c r="AK116" s="12"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8.1</t>
+        </is>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 스키마 검증 · 정규화</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-12·ANL-16</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-17</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-18</t>
+        </is>
+      </c>
+      <c r="I117" s="5">
+        <v>2</v>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드·단위테스트</t>
+        </is>
+      </c>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
+      <c r="N117" s="11"/>
+      <c r="O117" s="11"/>
+      <c r="P117" s="10"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="11"/>
+      <c r="S117" s="11"/>
+      <c r="T117" s="11"/>
+      <c r="U117" s="11"/>
+      <c r="V117" s="11"/>
+      <c r="W117" s="11"/>
+      <c r="X117" s="11"/>
+      <c r="Y117" s="11"/>
+      <c r="Z117" s="11"/>
+      <c r="AA117" s="11"/>
+      <c r="AB117" s="11"/>
+      <c r="AC117" s="11"/>
+      <c r="AD117" s="11"/>
+      <c r="AE117" s="11"/>
+      <c r="AF117" s="11"/>
+      <c r="AG117" s="11"/>
+      <c r="AH117" s="11"/>
+      <c r="AI117" s="11"/>
+      <c r="AJ117" s="12"/>
+      <c r="AK117" s="12"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8.2</t>
+        </is>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가·원가구분 컬럼 (리비전 0008)</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-13</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-18</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-18</t>
+        </is>
+      </c>
+      <c r="I118" s="5">
+        <v>1</v>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마이그레이션</t>
+        </is>
+      </c>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11"/>
+      <c r="O118" s="11"/>
+      <c r="P118" s="11"/>
+      <c r="Q118" s="10"/>
+      <c r="R118" s="11"/>
+      <c r="S118" s="11"/>
+      <c r="T118" s="11"/>
+      <c r="U118" s="11"/>
+      <c r="V118" s="11"/>
+      <c r="W118" s="11"/>
+      <c r="X118" s="11"/>
+      <c r="Y118" s="11"/>
+      <c r="Z118" s="11"/>
+      <c r="AA118" s="11"/>
+      <c r="AB118" s="11"/>
+      <c r="AC118" s="11"/>
+      <c r="AD118" s="11"/>
+      <c r="AE118" s="11"/>
+      <c r="AF118" s="11"/>
+      <c r="AG118" s="11"/>
+      <c r="AH118" s="11"/>
+      <c r="AI118" s="11"/>
+      <c r="AJ118" s="12"/>
+      <c r="AK118" s="12"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8.3</t>
+        </is>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비용 산출 엔진 · 계산식 표시</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-14·AMT-17</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-19</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-21</t>
+        </is>
+      </c>
+      <c r="I119" s="5">
+        <v>3</v>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드·단위테스트</t>
+        </is>
+      </c>
+      <c r="K119" s="11"/>
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
+      <c r="N119" s="11"/>
+      <c r="O119" s="11"/>
+      <c r="P119" s="11"/>
+      <c r="Q119" s="11"/>
+      <c r="R119" s="10"/>
+      <c r="S119" s="10"/>
+      <c r="T119" s="10"/>
+      <c r="U119" s="11"/>
+      <c r="V119" s="11"/>
+      <c r="W119" s="11"/>
+      <c r="X119" s="11"/>
+      <c r="Y119" s="11"/>
+      <c r="Z119" s="11"/>
+      <c r="AA119" s="11"/>
+      <c r="AB119" s="11"/>
+      <c r="AC119" s="11"/>
+      <c r="AD119" s="11"/>
+      <c r="AE119" s="11"/>
+      <c r="AF119" s="11"/>
+      <c r="AG119" s="11"/>
+      <c r="AH119" s="11"/>
+      <c r="AI119" s="11"/>
+      <c r="AJ119" s="12"/>
+      <c r="AK119" s="12"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8.4</t>
+        </is>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">평가셋 정확도 측정 자동화</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-17</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-20</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-21</t>
+        </is>
+      </c>
+      <c r="I120" s="5">
+        <v>2</v>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">측정 도구</t>
+        </is>
+      </c>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="11"/>
+      <c r="O120" s="11"/>
+      <c r="P120" s="11"/>
+      <c r="Q120" s="11"/>
+      <c r="R120" s="11"/>
+      <c r="S120" s="10"/>
+      <c r="T120" s="10"/>
+      <c r="U120" s="11"/>
+      <c r="V120" s="11"/>
+      <c r="W120" s="11"/>
+      <c r="X120" s="11"/>
+      <c r="Y120" s="11"/>
+      <c r="Z120" s="11"/>
+      <c r="AA120" s="11"/>
+      <c r="AB120" s="11"/>
+      <c r="AC120" s="11"/>
+      <c r="AD120" s="11"/>
+      <c r="AE120" s="11"/>
+      <c r="AF120" s="11"/>
+      <c r="AG120" s="11"/>
+      <c r="AH120" s="11"/>
+      <c r="AI120" s="11"/>
+      <c r="AJ120" s="12"/>
+      <c r="AK120" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J111"/>
+  <autoFilter ref="A3:J120"/>
   <pageMargins left="0.2" right="0.2" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8970,7 +9547,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -8987,7 +9564,7 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -9004,7 +9581,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -9021,7 +9598,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -9062,13 +9639,13 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C19" s="5">
         <v>27</v>
       </c>
       <c r="D19" s="5">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -9079,13 +9656,13 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C20" s="5">
         <v>27</v>
       </c>
       <c r="D20" s="5">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -9096,13 +9673,13 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5">
         <v>27</v>
       </c>
       <c r="D21" s="5">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E21" s="4"/>
     </row>
